--- a/artfynd/A 21364-2024 artfynd.xlsx
+++ b/artfynd/A 21364-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133218893</v>
+        <v>133218525</v>
       </c>
       <c r="B2" t="n">
-        <v>91977</v>
+        <v>93305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584354</v>
+        <v>584348</v>
       </c>
       <c r="R2" t="n">
-        <v>7029507</v>
+        <v>7029465</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -741,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133218890</v>
+        <v>133218526</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -882,6 +886,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133218527</v>
+      </c>
+      <c r="B4" t="n">
+        <v>108274</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gröningsåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>584354</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7029502</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21364-2024 artfynd.xlsx
+++ b/artfynd/A 21364-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133218525</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133218526</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,8 +1008,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133218527</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>